--- a/companies/alder-ridge/source-files/Shared/Finance/Treasury/FY27 working/treasury outlook support - July v6 pre-bank.xlsx
+++ b/companies/alder-ridge/source-files/Shared/Finance/Treasury/FY27 working/treasury outlook support - July v6 pre-bank.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Rb77fa7974c6a48dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash and Liquidity" sheetId="2" r:id="R14e6f23461724c45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and Hedges" sheetId="3" r:id="R9de706f1449c4e29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Economics" sheetId="4" r:id="R950b607871e145e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Outlook" sheetId="5" r:id="Rb84aaa3b8b794b40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Checks" sheetId="6" r:id="Rc375f5342f2a4794"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Ra2d8a64b3f1a4569"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash and Liquidity" sheetId="2" r:id="R43eb9cb0bd474f0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt and Hedges" sheetId="3" r:id="R7bfc1cedf02f4f61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Economics" sheetId="4" r:id="Ra83b75abda8446f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Outlook" sheetId="5" r:id="R6c73ad7ede564aef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Checks" sheetId="6" r:id="Rc468ac95279d4843"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -275,7 +275,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Alder Ridge Finance" id="{84F2A670-F2D9-4D6F-ACE0-68A35F188503}"/>
+  <xltc:person displayName="Alder Ridge Finance" id="{1B9771AE-2BF9-4349-99AA-84185A620C55}"/>
 </xltc:personList>
 </file>
 
@@ -1974,7 +1974,7 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="37" t="str">
-        <x:v>TRY-00534</x:v>
+        <x:v>TRY-00552</x:v>
       </x:c>
       <x:c r="B41" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2011,7 +2011,7 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="37" t="str">
-        <x:v>TRY-00535</x:v>
+        <x:v>TRY-00553</x:v>
       </x:c>
       <x:c r="B42" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2048,7 +2048,7 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="37" t="str">
-        <x:v>TRY-00536</x:v>
+        <x:v>TRY-00554</x:v>
       </x:c>
       <x:c r="B43" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2085,7 +2085,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="37" t="str">
-        <x:v>TRY-00537</x:v>
+        <x:v>TRY-00555</x:v>
       </x:c>
       <x:c r="B44" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2122,7 +2122,7 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="37" t="str">
-        <x:v>TRY-00538</x:v>
+        <x:v>TRY-00556</x:v>
       </x:c>
       <x:c r="B45" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2159,7 +2159,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="37" t="str">
-        <x:v>TRY-00539</x:v>
+        <x:v>TRY-00557</x:v>
       </x:c>
       <x:c r="B46" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2196,7 +2196,7 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="37" t="str">
-        <x:v>TRY-00540</x:v>
+        <x:v>TRY-00558</x:v>
       </x:c>
       <x:c r="B47" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2233,7 +2233,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="37" t="str">
-        <x:v>TRY-00541</x:v>
+        <x:v>TRY-00559</x:v>
       </x:c>
       <x:c r="B48" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2270,7 +2270,7 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="37" t="str">
-        <x:v>TRY-00542</x:v>
+        <x:v>TRY-00560</x:v>
       </x:c>
       <x:c r="B49" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2307,7 +2307,7 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="37" t="str">
-        <x:v>TRY-00543</x:v>
+        <x:v>TRY-00561</x:v>
       </x:c>
       <x:c r="B50" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2344,7 +2344,7 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="37" t="str">
-        <x:v>TRY-00544</x:v>
+        <x:v>TRY-00562</x:v>
       </x:c>
       <x:c r="B51" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2381,7 +2381,7 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="37" t="str">
-        <x:v>TRY-00545</x:v>
+        <x:v>TRY-00563</x:v>
       </x:c>
       <x:c r="B52" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2418,7 +2418,7 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="37" t="str">
-        <x:v>TRY-00546</x:v>
+        <x:v>TRY-00564</x:v>
       </x:c>
       <x:c r="B53" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2455,7 +2455,7 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="37" t="str">
-        <x:v>TRY-00547</x:v>
+        <x:v>TRY-00565</x:v>
       </x:c>
       <x:c r="B54" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2492,7 +2492,7 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="37" t="str">
-        <x:v>TRY-00548</x:v>
+        <x:v>TRY-00566</x:v>
       </x:c>
       <x:c r="B55" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2529,7 +2529,7 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="37" t="str">
-        <x:v>TRY-00549</x:v>
+        <x:v>TRY-00567</x:v>
       </x:c>
       <x:c r="B56" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2566,7 +2566,7 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="37" t="str">
-        <x:v>TRY-00593</x:v>
+        <x:v>TRY-00611</x:v>
       </x:c>
       <x:c r="B57" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2603,7 +2603,7 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="37" t="str">
-        <x:v>TRY-00594</x:v>
+        <x:v>TRY-00612</x:v>
       </x:c>
       <x:c r="B58" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2640,7 +2640,7 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="37" t="str">
-        <x:v>TRY-00595</x:v>
+        <x:v>TRY-00613</x:v>
       </x:c>
       <x:c r="B59" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2677,7 +2677,7 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="37" t="str">
-        <x:v>TRY-00596</x:v>
+        <x:v>TRY-00614</x:v>
       </x:c>
       <x:c r="B60" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2714,7 +2714,7 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="37" t="str">
-        <x:v>TRY-00597</x:v>
+        <x:v>TRY-00615</x:v>
       </x:c>
       <x:c r="B61" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2751,7 +2751,7 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="37" t="str">
-        <x:v>TRY-00598</x:v>
+        <x:v>TRY-00616</x:v>
       </x:c>
       <x:c r="B62" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2788,7 +2788,7 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="37" t="str">
-        <x:v>TRY-00599</x:v>
+        <x:v>TRY-00617</x:v>
       </x:c>
       <x:c r="B63" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2825,7 +2825,7 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="37" t="str">
-        <x:v>TRY-00600</x:v>
+        <x:v>TRY-00618</x:v>
       </x:c>
       <x:c r="B64" s="28" t="str">
         <x:v>Create the dynamic 13-week cash and revolver model</x:v>
@@ -2862,7 +2862,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="37" t="str">
-        <x:v>TRY-00835</x:v>
+        <x:v>TRY-00853</x:v>
       </x:c>
       <x:c r="B65" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -2899,7 +2899,7 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="37" t="str">
-        <x:v>TRY-00836</x:v>
+        <x:v>TRY-00854</x:v>
       </x:c>
       <x:c r="B66" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -2936,7 +2936,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="37" t="str">
-        <x:v>TRY-00837</x:v>
+        <x:v>TRY-00855</x:v>
       </x:c>
       <x:c r="B67" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -2973,7 +2973,7 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="37" t="str">
-        <x:v>TRY-00838</x:v>
+        <x:v>TRY-00856</x:v>
       </x:c>
       <x:c r="B68" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3010,7 +3010,7 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="37" t="str">
-        <x:v>TRY-00839</x:v>
+        <x:v>TRY-00857</x:v>
       </x:c>
       <x:c r="B69" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3047,7 +3047,7 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="37" t="str">
-        <x:v>TRY-00840</x:v>
+        <x:v>TRY-00858</x:v>
       </x:c>
       <x:c r="B70" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3084,7 +3084,7 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="37" t="str">
-        <x:v>TRY-00841</x:v>
+        <x:v>TRY-00859</x:v>
       </x:c>
       <x:c r="B71" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3121,7 +3121,7 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="37" t="str">
-        <x:v>TRY-00842</x:v>
+        <x:v>TRY-00860</x:v>
       </x:c>
       <x:c r="B72" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3158,7 +3158,7 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="37" t="str">
-        <x:v>TRY-00843</x:v>
+        <x:v>TRY-00861</x:v>
       </x:c>
       <x:c r="B73" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3195,7 +3195,7 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="37" t="str">
-        <x:v>TRY-00844</x:v>
+        <x:v>TRY-00862</x:v>
       </x:c>
       <x:c r="B74" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3232,7 +3232,7 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="37" t="str">
-        <x:v>TRY-00845</x:v>
+        <x:v>TRY-00863</x:v>
       </x:c>
       <x:c r="B75" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3269,7 +3269,7 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="37" t="str">
-        <x:v>TRY-00846</x:v>
+        <x:v>TRY-00864</x:v>
       </x:c>
       <x:c r="B76" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3306,7 +3306,7 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="37" t="str">
-        <x:v>TRY-00868</x:v>
+        <x:v>TRY-00886</x:v>
       </x:c>
       <x:c r="B77" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3343,7 +3343,7 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="37" t="str">
-        <x:v>TRY-00869</x:v>
+        <x:v>TRY-00887</x:v>
       </x:c>
       <x:c r="B78" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3380,7 +3380,7 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="37" t="str">
-        <x:v>TRY-00870</x:v>
+        <x:v>TRY-00888</x:v>
       </x:c>
       <x:c r="B79" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3417,7 +3417,7 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="37" t="str">
-        <x:v>TRY-00871</x:v>
+        <x:v>TRY-00889</x:v>
       </x:c>
       <x:c r="B80" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3454,7 +3454,7 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="37" t="str">
-        <x:v>TRY-00872</x:v>
+        <x:v>TRY-00890</x:v>
       </x:c>
       <x:c r="B81" s="28" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -3491,7 +3491,7 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="38" t="str">
-        <x:v>TRY-00873</x:v>
+        <x:v>TRY-00891</x:v>
       </x:c>
       <x:c r="B82" s="29" t="str">
         <x:v>Cash-investment liquidity ladder</x:v>
@@ -4741,7 +4741,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="37" t="str">
-        <x:v>TRY-00633</x:v>
+        <x:v>TRY-00651</x:v>
       </x:c>
       <x:c r="B35" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -4778,7 +4778,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="37" t="str">
-        <x:v>TRY-00634</x:v>
+        <x:v>TRY-00652</x:v>
       </x:c>
       <x:c r="B36" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -4815,7 +4815,7 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="37" t="str">
-        <x:v>TRY-00635</x:v>
+        <x:v>TRY-00653</x:v>
       </x:c>
       <x:c r="B37" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -4852,7 +4852,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="37" t="str">
-        <x:v>TRY-00636</x:v>
+        <x:v>TRY-00654</x:v>
       </x:c>
       <x:c r="B38" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -4889,7 +4889,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="37" t="str">
-        <x:v>TRY-00637</x:v>
+        <x:v>TRY-00655</x:v>
       </x:c>
       <x:c r="B39" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -4926,7 +4926,7 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="37" t="str">
-        <x:v>TRY-00638</x:v>
+        <x:v>TRY-00656</x:v>
       </x:c>
       <x:c r="B40" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -4963,7 +4963,7 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="37" t="str">
-        <x:v>TRY-00639</x:v>
+        <x:v>TRY-00657</x:v>
       </x:c>
       <x:c r="B41" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5000,7 +5000,7 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="37" t="str">
-        <x:v>TRY-00640</x:v>
+        <x:v>TRY-00658</x:v>
       </x:c>
       <x:c r="B42" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5037,7 +5037,7 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="37" t="str">
-        <x:v>TRY-00641</x:v>
+        <x:v>TRY-00659</x:v>
       </x:c>
       <x:c r="B43" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5074,7 +5074,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="37" t="str">
-        <x:v>TRY-00642</x:v>
+        <x:v>TRY-00660</x:v>
       </x:c>
       <x:c r="B44" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5111,7 +5111,7 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="37" t="str">
-        <x:v>TRY-00643</x:v>
+        <x:v>TRY-00661</x:v>
       </x:c>
       <x:c r="B45" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5148,7 +5148,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="37" t="str">
-        <x:v>TRY-00644</x:v>
+        <x:v>TRY-00662</x:v>
       </x:c>
       <x:c r="B46" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5185,7 +5185,7 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="37" t="str">
-        <x:v>TRY-00645</x:v>
+        <x:v>TRY-00663</x:v>
       </x:c>
       <x:c r="B47" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5222,7 +5222,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="37" t="str">
-        <x:v>TRY-00646</x:v>
+        <x:v>TRY-00664</x:v>
       </x:c>
       <x:c r="B48" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5259,7 +5259,7 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="37" t="str">
-        <x:v>TRY-00660</x:v>
+        <x:v>TRY-00678</x:v>
       </x:c>
       <x:c r="B49" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5296,7 +5296,7 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="37" t="str">
-        <x:v>TRY-00661</x:v>
+        <x:v>TRY-00679</x:v>
       </x:c>
       <x:c r="B50" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5333,7 +5333,7 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="37" t="str">
-        <x:v>TRY-00662</x:v>
+        <x:v>TRY-00680</x:v>
       </x:c>
       <x:c r="B51" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5370,7 +5370,7 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="37" t="str">
-        <x:v>TRY-00663</x:v>
+        <x:v>TRY-00681</x:v>
       </x:c>
       <x:c r="B52" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5407,7 +5407,7 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="37" t="str">
-        <x:v>TRY-00664</x:v>
+        <x:v>TRY-00682</x:v>
       </x:c>
       <x:c r="B53" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5444,7 +5444,7 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="37" t="str">
-        <x:v>TRY-00665</x:v>
+        <x:v>TRY-00683</x:v>
       </x:c>
       <x:c r="B54" s="28" t="str">
         <x:v>Refinancing, hedge, and covenant economics</x:v>
@@ -5481,7 +5481,7 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="37" t="str">
-        <x:v>TRY-00695</x:v>
+        <x:v>TRY-00713</x:v>
       </x:c>
       <x:c r="B55" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5518,7 +5518,7 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="37" t="str">
-        <x:v>TRY-00696</x:v>
+        <x:v>TRY-00714</x:v>
       </x:c>
       <x:c r="B56" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5555,7 +5555,7 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="37" t="str">
-        <x:v>TRY-00697</x:v>
+        <x:v>TRY-00715</x:v>
       </x:c>
       <x:c r="B57" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5592,7 +5592,7 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="37" t="str">
-        <x:v>TRY-00698</x:v>
+        <x:v>TRY-00716</x:v>
       </x:c>
       <x:c r="B58" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5629,7 +5629,7 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="37" t="str">
-        <x:v>TRY-00699</x:v>
+        <x:v>TRY-00717</x:v>
       </x:c>
       <x:c r="B59" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5666,7 +5666,7 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="37" t="str">
-        <x:v>TRY-00700</x:v>
+        <x:v>TRY-00718</x:v>
       </x:c>
       <x:c r="B60" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5703,7 +5703,7 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="37" t="str">
-        <x:v>TRY-00701</x:v>
+        <x:v>TRY-00719</x:v>
       </x:c>
       <x:c r="B61" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5740,7 +5740,7 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="37" t="str">
-        <x:v>TRY-00702</x:v>
+        <x:v>TRY-00720</x:v>
       </x:c>
       <x:c r="B62" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5777,7 +5777,7 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="37" t="str">
-        <x:v>TRY-00703</x:v>
+        <x:v>TRY-00721</x:v>
       </x:c>
       <x:c r="B63" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5814,7 +5814,7 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="37" t="str">
-        <x:v>TRY-00704</x:v>
+        <x:v>TRY-00722</x:v>
       </x:c>
       <x:c r="B64" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5851,7 +5851,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="37" t="str">
-        <x:v>TRY-00705</x:v>
+        <x:v>TRY-00723</x:v>
       </x:c>
       <x:c r="B65" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5888,7 +5888,7 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="37" t="str">
-        <x:v>TRY-00706</x:v>
+        <x:v>TRY-00724</x:v>
       </x:c>
       <x:c r="B66" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5925,7 +5925,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="37" t="str">
-        <x:v>TRY-00714</x:v>
+        <x:v>TRY-00732</x:v>
       </x:c>
       <x:c r="B67" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5962,7 +5962,7 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="37" t="str">
-        <x:v>TRY-00715</x:v>
+        <x:v>TRY-00733</x:v>
       </x:c>
       <x:c r="B68" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -5999,7 +5999,7 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="37" t="str">
-        <x:v>TRY-00716</x:v>
+        <x:v>TRY-00734</x:v>
       </x:c>
       <x:c r="B69" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -6036,7 +6036,7 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="37" t="str">
-        <x:v>TRY-00717</x:v>
+        <x:v>TRY-00735</x:v>
       </x:c>
       <x:c r="B70" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -6073,7 +6073,7 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="37" t="str">
-        <x:v>TRY-00718</x:v>
+        <x:v>TRY-00736</x:v>
       </x:c>
       <x:c r="B71" s="28" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -6110,7 +6110,7 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="38" t="str">
-        <x:v>TRY-00719</x:v>
+        <x:v>TRY-00737</x:v>
       </x:c>
       <x:c r="B72" s="29" t="str">
         <x:v>Layered FX hedge plan</x:v>
@@ -6620,7 +6620,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="37" t="str">
-        <x:v>TRY-00467</x:v>
+        <x:v>TRY-00485</x:v>
       </x:c>
       <x:c r="B15" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -6657,7 +6657,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="37" t="str">
-        <x:v>TRY-00468</x:v>
+        <x:v>TRY-00486</x:v>
       </x:c>
       <x:c r="B16" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -6694,7 +6694,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="37" t="str">
-        <x:v>TRY-00469</x:v>
+        <x:v>TRY-00487</x:v>
       </x:c>
       <x:c r="B17" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -6731,7 +6731,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="37" t="str">
-        <x:v>TRY-00470</x:v>
+        <x:v>TRY-00488</x:v>
       </x:c>
       <x:c r="B18" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -6768,7 +6768,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="37" t="str">
-        <x:v>TRY-00471</x:v>
+        <x:v>TRY-00489</x:v>
       </x:c>
       <x:c r="B19" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -6805,7 +6805,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="37" t="str">
-        <x:v>TRY-00472</x:v>
+        <x:v>TRY-00490</x:v>
       </x:c>
       <x:c r="B20" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -6842,7 +6842,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="37" t="str">
-        <x:v>TRY-00473</x:v>
+        <x:v>TRY-00491</x:v>
       </x:c>
       <x:c r="B21" s="28" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -6879,7 +6879,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="38" t="str">
-        <x:v>TRY-00474</x:v>
+        <x:v>TRY-00492</x:v>
       </x:c>
       <x:c r="B22" s="29" t="str">
         <x:v>Bank relationship profitability scorecard</x:v>
@@ -7019,10 +7019,10 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="36" t="str">
-        <x:v>TRY-00413</x:v>
+        <x:v>TRY-00431</x:v>
       </x:c>
       <x:c r="B5" s="27" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C5" s="27" t="str">
         <x:v>Debt Schedule</x:v>
@@ -7056,10 +7056,10 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="37" t="str">
-        <x:v>TRY-00414</x:v>
+        <x:v>TRY-00432</x:v>
       </x:c>
       <x:c r="B6" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C6" s="28" t="str">
         <x:v>Forecast Inputs</x:v>
@@ -7077,11 +7077,11 @@
         <x:v>Quarterly covenant EBITDA</x:v>
       </x:c>
       <x:c r="H6" s="31" t="n">
-        <x:v>3203200</x:v>
+        <x:v>3203.2</x:v>
       </x:c>
       <x:c r="I6" s="28" t="str"/>
       <x:c r="J6" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K6" s="28" t="str">
         <x:v>Earlier management working export</x:v>
@@ -7093,10 +7093,10 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="37" t="str">
-        <x:v>TRY-00415</x:v>
+        <x:v>TRY-00433</x:v>
       </x:c>
       <x:c r="B7" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C7" s="28" t="str">
         <x:v>Forecast Inputs</x:v>
@@ -7130,10 +7130,10 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="37" t="str">
-        <x:v>TRY-00416</x:v>
+        <x:v>TRY-00434</x:v>
       </x:c>
       <x:c r="B8" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C8" s="28" t="str">
         <x:v>Forecast Inputs</x:v>
@@ -7151,11 +7151,11 @@
         <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="H8" s="31" t="n">
-        <x:v>896.1</x:v>
+        <x:v>896100</x:v>
       </x:c>
       <x:c r="I8" s="28" t="str"/>
       <x:c r="J8" s="28" t="str">
-        <x:v>USD thousands</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K8" s="28" t="str">
         <x:v>Earlier management working export</x:v>
@@ -7167,10 +7167,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="37" t="str">
-        <x:v>TRY-00417</x:v>
+        <x:v>TRY-00435</x:v>
       </x:c>
       <x:c r="B9" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C9" s="28" t="str">
         <x:v>Forecast Inputs</x:v>
@@ -7204,10 +7204,10 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="37" t="str">
-        <x:v>TRY-00418</x:v>
+        <x:v>TRY-00436</x:v>
       </x:c>
       <x:c r="B10" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C10" s="28" t="str">
         <x:v>Forecast Inputs</x:v>
@@ -7225,11 +7225,11 @@
         <x:v>Distributions</x:v>
       </x:c>
       <x:c r="H10" s="31" t="n">
-        <x:v>105000</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="I10" s="28" t="str"/>
       <x:c r="J10" s="28" t="str">
-        <x:v>USD</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="K10" s="28" t="str">
         <x:v>Earlier management working export</x:v>
@@ -7241,10 +7241,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="37" t="str">
-        <x:v>TRY-00419</x:v>
+        <x:v>TRY-00437</x:v>
       </x:c>
       <x:c r="B11" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C11" s="28" t="str">
         <x:v>Forecast Inputs</x:v>
@@ -7278,10 +7278,10 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="37" t="str">
-        <x:v>TRY-00420</x:v>
+        <x:v>TRY-00438</x:v>
       </x:c>
       <x:c r="B12" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C12" s="28" t="str">
         <x:v>Covenant policy</x:v>
@@ -7315,13 +7315,13 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="37" t="str">
-        <x:v>TRY-00421</x:v>
+        <x:v>TRY-00439</x:v>
       </x:c>
       <x:c r="B13" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C13" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D13" s="28" t="str">
         <x:v>Consolidated</x:v>
@@ -7330,13 +7330,13 @@
         <x:v>2026-05 working copy</x:v>
       </x:c>
       <x:c r="F13" s="28" t="str">
-        <x:v>Actual</x:v>
+        <x:v>Downside</x:v>
       </x:c>
       <x:c r="G13" s="28" t="str">
-        <x:v>Scheduled debt repayment</x:v>
+        <x:v>Cash interest increment</x:v>
       </x:c>
       <x:c r="H13" s="31" t="n">
-        <x:v>682500</x:v>
+        <x:v>78750</x:v>
       </x:c>
       <x:c r="I13" s="28" t="str"/>
       <x:c r="J13" s="28" t="str">
@@ -7352,28 +7352,28 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="37" t="str">
-        <x:v>TRY-00422</x:v>
+        <x:v>TRY-00440</x:v>
       </x:c>
       <x:c r="B14" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C14" s="28" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
+        <x:v>Covenant Downside</x:v>
       </x:c>
       <x:c r="D14" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E14" s="28" t="str">
-        <x:v>2026-Q2</x:v>
+        <x:v>2027-Q3</x:v>
       </x:c>
       <x:c r="F14" s="28" t="str">
         <x:v>Management stretch</x:v>
       </x:c>
       <x:c r="G14" s="28" t="str">
-        <x:v>Cash interest</x:v>
+        <x:v>Unfunded capex increment</x:v>
       </x:c>
       <x:c r="H14" s="31" t="n">
-        <x:v>465560</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I14" s="28" t="str"/>
       <x:c r="J14" s="28" t="str">
@@ -7389,13 +7389,13 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="37" t="str">
-        <x:v>TRY-00423</x:v>
+        <x:v>TRY-00441</x:v>
       </x:c>
       <x:c r="B15" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C15" s="28" t="str">
-        <x:v>Forecast Inputs</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D15" s="28" t="str">
         <x:v>Consolidated</x:v>
@@ -7404,13 +7404,13 @@
         <x:v>2026-05 working copy</x:v>
       </x:c>
       <x:c r="F15" s="28" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Actual</x:v>
       </x:c>
       <x:c r="G15" s="28" t="str">
-        <x:v>Unfunded capital expenditures</x:v>
+        <x:v>Quarterly covenant EBITDA</x:v>
       </x:c>
       <x:c r="H15" s="31" t="n">
-        <x:v>644800</x:v>
+        <x:v>2964000</x:v>
       </x:c>
       <x:c r="I15" s="28" t="str"/>
       <x:c r="J15" s="28" t="str">
@@ -7426,32 +7426,32 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="37" t="str">
-        <x:v>TRY-00424</x:v>
+        <x:v>TRY-00442</x:v>
       </x:c>
       <x:c r="B16" s="28" t="str">
-        <x:v>Complete the eight-quarter covenant forecast</x:v>
+        <x:v>FY27 covenant outlook</x:v>
       </x:c>
       <x:c r="C16" s="28" t="str">
-        <x:v>Forecast Inputs</x:v>
+        <x:v>Historical Covenant Inputs</x:v>
       </x:c>
       <x:c r="D16" s="28" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="E16" s="28" t="str">
-        <x:v>2026-Q4</x:v>
+        <x:v>2026-Q1</x:v>
       </x:c>
       <x:c r="F16" s="28" t="str">
         <x:v>Management stretch</x:v>
       </x:c>
       <x:c r="G16" s="28" t="str">
-        <x:v>Cash taxes</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="H16" s="31" t="n">
-        <x:v>338.1</x:v>
+        <x:v>640500</x:v>
       </x:c>
       <x:c r="I16" s="28" t="str"/>
       <x:c r="J16" s="28" t="str">
-        <x:v>USD thousands</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K16" s="28" t="str">
         <x:v>Earlier management working export</x:v>
@@ -7463,7 +7463,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="37" t="str">
-        <x:v>TRY-00440</x:v>
+        <x:v>TRY-00458</x:v>
       </x:c>
       <x:c r="B17" s="28" t="str">
         <x:v>Credit metrics and incremental debt capacity</x:v>
@@ -7500,7 +7500,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="37" t="str">
-        <x:v>TRY-00441</x:v>
+        <x:v>TRY-00459</x:v>
       </x:c>
       <x:c r="B18" s="28" t="str">
         <x:v>Credit metrics and incremental debt capacity</x:v>
@@ -7537,7 +7537,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="37" t="str">
-        <x:v>TRY-00442</x:v>
+        <x:v>TRY-00460</x:v>
       </x:c>
       <x:c r="B19" s="28" t="str">
         <x:v>Credit metrics and incremental debt capacity</x:v>
@@ -7574,7 +7574,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="37" t="str">
-        <x:v>TRY-00443</x:v>
+        <x:v>TRY-00461</x:v>
       </x:c>
       <x:c r="B20" s="28" t="str">
         <x:v>Credit metrics and incremental debt capacity</x:v>
@@ -7611,7 +7611,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="37" t="str">
-        <x:v>TRY-00444</x:v>
+        <x:v>TRY-00462</x:v>
       </x:c>
       <x:c r="B21" s="28" t="str">
         <x:v>Credit metrics and incremental debt capacity</x:v>
@@ -7648,7 +7648,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="37" t="str">
-        <x:v>TRY-00445</x:v>
+        <x:v>TRY-00463</x:v>
       </x:c>
       <x:c r="B22" s="28" t="str">
         <x:v>Credit metrics and incremental debt capacity</x:v>
@@ -7685,7 +7685,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="37" t="str">
-        <x:v>TRY-00446</x:v>
+        <x:v>TRY-00464</x:v>
       </x:c>
       <x:c r="B23" s="28" t="str">
         <x:v>Credit metrics and incremental debt capacity</x:v>
@@ -7722,7 +7722,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="37" t="str">
-        <x:v>TRY-00447</x:v>
+        <x:v>TRY-00465</x:v>
       </x:c>
       <x:c r="B24" s="28" t="str">
         <x:v>Credit metrics and incremental debt capacity</x:v>
@@ -7759,7 +7759,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="37" t="str">
-        <x:v>TRY-00745</x:v>
+        <x:v>TRY-00763</x:v>
       </x:c>
       <x:c r="B25" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -7796,7 +7796,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="37" t="str">
-        <x:v>TRY-00746</x:v>
+        <x:v>TRY-00764</x:v>
       </x:c>
       <x:c r="B26" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -7833,7 +7833,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="37" t="str">
-        <x:v>TRY-00747</x:v>
+        <x:v>TRY-00765</x:v>
       </x:c>
       <x:c r="B27" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -7870,7 +7870,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="37" t="str">
-        <x:v>TRY-00748</x:v>
+        <x:v>TRY-00766</x:v>
       </x:c>
       <x:c r="B28" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -7907,7 +7907,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="37" t="str">
-        <x:v>TRY-00749</x:v>
+        <x:v>TRY-00767</x:v>
       </x:c>
       <x:c r="B29" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -7944,7 +7944,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="37" t="str">
-        <x:v>TRY-00750</x:v>
+        <x:v>TRY-00768</x:v>
       </x:c>
       <x:c r="B30" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -7981,7 +7981,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="37" t="str">
-        <x:v>TRY-00751</x:v>
+        <x:v>TRY-00769</x:v>
       </x:c>
       <x:c r="B31" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -8018,7 +8018,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="37" t="str">
-        <x:v>TRY-00752</x:v>
+        <x:v>TRY-00770</x:v>
       </x:c>
       <x:c r="B32" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -8055,7 +8055,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="37" t="str">
-        <x:v>TRY-00753</x:v>
+        <x:v>TRY-00771</x:v>
       </x:c>
       <x:c r="B33" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -8092,7 +8092,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="37" t="str">
-        <x:v>TRY-00754</x:v>
+        <x:v>TRY-00772</x:v>
       </x:c>
       <x:c r="B34" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -8129,7 +8129,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="37" t="str">
-        <x:v>TRY-00755</x:v>
+        <x:v>TRY-00773</x:v>
       </x:c>
       <x:c r="B35" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -8166,7 +8166,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="37" t="str">
-        <x:v>TRY-00756</x:v>
+        <x:v>TRY-00774</x:v>
       </x:c>
       <x:c r="B36" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -8203,7 +8203,7 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="37" t="str">
-        <x:v>TRY-00757</x:v>
+        <x:v>TRY-00775</x:v>
       </x:c>
       <x:c r="B37" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -8240,7 +8240,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="37" t="str">
-        <x:v>TRY-00758</x:v>
+        <x:v>TRY-00776</x:v>
       </x:c>
       <x:c r="B38" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -8277,7 +8277,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="37" t="str">
-        <x:v>TRY-00791</x:v>
+        <x:v>TRY-00809</x:v>
       </x:c>
       <x:c r="B39" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -8314,7 +8314,7 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="37" t="str">
-        <x:v>TRY-00792</x:v>
+        <x:v>TRY-00810</x:v>
       </x:c>
       <x:c r="B40" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -8351,7 +8351,7 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="37" t="str">
-        <x:v>TRY-00793</x:v>
+        <x:v>TRY-00811</x:v>
       </x:c>
       <x:c r="B41" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -8388,7 +8388,7 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="37" t="str">
-        <x:v>TRY-00794</x:v>
+        <x:v>TRY-00812</x:v>
       </x:c>
       <x:c r="B42" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -8425,7 +8425,7 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="37" t="str">
-        <x:v>TRY-00795</x:v>
+        <x:v>TRY-00813</x:v>
       </x:c>
       <x:c r="B43" s="28" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
@@ -8462,7 +8462,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="38" t="str">
-        <x:v>TRY-00796</x:v>
+        <x:v>TRY-00814</x:v>
       </x:c>
       <x:c r="B44" s="29" t="str">
         <x:v>ABL borrowing base and covenant cure</x:v>
